--- a/python-excel-capm-demo.xlsx
+++ b/python-excel-capm-demo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\blog-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2000001_{F5FB3746-3935-488C-B829-3580CA6E0994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F0F0CD7-EA5A-4B90-8457-2452AD8C179B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -274,8 +274,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -319,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -335,6 +336,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -381,8 +384,8 @@
       <xdr:rowOff>156633</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>137205</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>649438</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>148166</xdr:rowOff>
     </xdr:to>
@@ -430,8 +433,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>122305</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>634539</xdr:colOff>
       <xdr:row>67</xdr:row>
       <xdr:rowOff>118534</xdr:rowOff>
     </xdr:to>
@@ -646,11 +649,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PriceData" displayName="PriceData" ref="A1:C261" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PriceData" displayName="PriceData" ref="A1:C261" headerRowDxfId="5" dataDxfId="4" totalsRowDxfId="3">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Market_ETF_Close" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="TechCo_Close" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Market_ETF_Close" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="TechCo_Close" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -810,6 +813,8 @@
   <cols>
     <col min="1" max="3" width="15.6640625" style="6" customWidth="1"/>
     <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.609375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.35">
@@ -1018,10 +1023,10 @@
       <c r="E11" vm="2">
         <v>45294</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="7">
         <v>-0.43092715880987953</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="7">
         <v>-2.5386186390415233</v>
       </c>
     </row>
@@ -1038,10 +1043,10 @@
       <c r="E12" vm="3">
         <v>45295</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="7">
         <v>1.5941355817806091</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="7">
         <v>5.4686055435277936</v>
       </c>
     </row>
@@ -1058,10 +1063,10 @@
       <c r="E13" vm="4">
         <v>45296</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="7">
         <v>0.58148293740130086</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="7">
         <v>2.2406673277330924</v>
       </c>
     </row>
@@ -1078,10 +1083,10 @@
       <c r="E14" vm="5">
         <v>45299</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="7">
         <v>1.521386863582741</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="7">
         <v>2.8336165351342757</v>
       </c>
     </row>
@@ -1098,10 +1103,10 @@
       <c r="E15" vm="6">
         <v>45300</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="7">
         <v>1.0015492040888141</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="7">
         <v>2.5877651242804056</v>
       </c>
     </row>
@@ -1130,7 +1135,7 @@
         <f t="array" ref="E17:F17">_xlfn._xlws.PY(2,0)</f>
         <v>market_rtn</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="8">
         <v>1.1894246844953897</v>
       </c>
     </row>
@@ -1497,7 +1502,7 @@
       <c r="E44" t="str">
         <v>mean</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="7">
         <v>1.1878269121702383</v>
       </c>
     </row>
@@ -1514,7 +1519,7 @@
       <c r="E45" t="str">
         <v>std</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="7">
         <v>7.3172547663813953E-2</v>
       </c>
     </row>
@@ -1531,7 +1536,7 @@
       <c r="E46" t="str">
         <v>min</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="7">
         <v>0.86718532635466605</v>
       </c>
     </row>
@@ -1548,7 +1553,7 @@
       <c r="E47" t="str">
         <v>25%</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="7">
         <v>1.1374012857699654</v>
       </c>
     </row>
@@ -1565,7 +1570,7 @@
       <c r="E48" t="str">
         <v>50%</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="7">
         <v>1.1885858694989979</v>
       </c>
     </row>
@@ -1582,7 +1587,7 @@
       <c r="E49" t="str">
         <v>75%</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="7">
         <v>1.236923720916602</v>
       </c>
     </row>
@@ -1599,7 +1604,7 @@
       <c r="E50" t="str">
         <v>max</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="7">
         <v>1.4183507229486714</v>
       </c>
     </row>
